--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Lokale Codes für Senologie-Verlaufsmeldungen (OncoBox M01-M10). Enthält Komponentenbezeichner und Wertcodes für Felder ohne SNOMED-CT-Äquivalent.</t>
+    <t>Lokale Codes für Senologie-Verlaufsmeldungen (OncoBox M01-M10). Enthält Codes für Observation.method (Nachsorge-Art), Zweittumor-Komponentencode und Wertcodes.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>7</t>
+    <t>3</t>
   </si>
   <si>
     <t>Level</t>
@@ -138,24 +138,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>nachsorge-art</t>
-  </si>
-  <si>
-    <t>Art der Nachsorge</t>
-  </si>
-  <si>
-    <t>Komponente: Aktive oder passive Nachsorge (M03)</t>
-  </si>
-  <si>
-    <t>vitalstatus</t>
-  </si>
-  <si>
-    <t>Vitalstatus</t>
-  </si>
-  <si>
-    <t>Komponente: Vitalstatus der Patientin zum Meldezeitpunkt (M04)</t>
-  </si>
-  <si>
     <t>zweittumor</t>
   </si>
   <si>
@@ -165,31 +147,13 @@
     <t>Komponente: Zweittumor ja/nein/unbekannt (M08)</t>
   </si>
   <si>
-    <t>zweittumor-icd</t>
-  </si>
-  <si>
-    <t>Zweittumor ICD-10-GM Diagnose</t>
-  </si>
-  <si>
-    <t>Komponente: ICD-10-GM-Code des Zweittumors (M09)</t>
-  </si>
-  <si>
-    <t>zweittumor-datum</t>
-  </si>
-  <si>
-    <t>Zweittumor Diagnosedatum</t>
-  </si>
-  <si>
-    <t>Komponente: Diagnosedatum des Zweittumors (M10)</t>
-  </si>
-  <si>
     <t>aktiv</t>
   </si>
   <si>
     <t>Aktive Nachsorge</t>
   </si>
   <si>
-    <t>Patientin wurde persönlich untersucht oder befragt</t>
+    <t>Patientin wurde persoenlich untersucht oder befragt</t>
   </si>
   <si>
     <t>passiv</t>
@@ -506,7 +470,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -565,62 +529,6 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>61</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
+++ b/ci-build/CodeSystem-cs-senologie-follow-up.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
